--- a/E/MBF04S.xlsx
+++ b/E/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="431">
   <si>
     <t/>
   </si>
@@ -463,6 +463,18 @@
     <t>YB BABY CRACK BNN 25</t>
   </si>
   <si>
+    <t>20143372</t>
+  </si>
+  <si>
+    <t>MNDE BRMN CKS BNNA40</t>
+  </si>
+  <si>
+    <t>20143371</t>
+  </si>
+  <si>
+    <t>MNDE BRMN CKS TMGO40</t>
+  </si>
+  <si>
     <t>20125783</t>
   </si>
   <si>
@@ -515,6 +527,12 @@
   </si>
   <si>
     <t>SUNBAY EVP.MILK 380G</t>
+  </si>
+  <si>
+    <t>20143301</t>
+  </si>
+  <si>
+    <t>INDMLK CRM MTCHA 260</t>
   </si>
   <si>
     <t>20136510</t>
@@ -1678,7 +1696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F195"/>
+  <dimension ref="A1:F198"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3020,10 +3038,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>16</v>
@@ -3040,10 +3058,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>16</v>
@@ -3063,10 +3081,10 @@
         <v>29</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3083,10 +3101,10 @@
         <v>29</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3103,7 +3121,7 @@
         <v>29</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>20</v>
@@ -3123,10 +3141,10 @@
         <v>29</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -3143,10 +3161,10 @@
         <v>29</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3163,7 +3181,7 @@
         <v>29</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>16</v>
@@ -3183,10 +3201,10 @@
         <v>29</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3200,13 +3218,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3220,13 +3238,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3240,10 +3258,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>16</v>
@@ -3263,10 +3281,10 @@
         <v>32</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3283,10 +3301,10 @@
         <v>32</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3303,10 +3321,10 @@
         <v>32</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3323,10 +3341,10 @@
         <v>32</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3340,13 +3358,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3360,10 +3378,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3380,13 +3398,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3403,7 +3421,7 @@
         <v>38</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3423,7 +3441,7 @@
         <v>38</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -3443,18 +3461,18 @@
         <v>38</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>194</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3463,18 +3481,18 @@
         <v>38</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>194</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3483,18 +3501,18 @@
         <v>38</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>194</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3503,10 +3521,10 @@
         <v>38</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3520,13 +3538,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3540,13 +3558,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3560,13 +3578,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3583,7 +3601,7 @@
         <v>134</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3603,10 +3621,10 @@
         <v>134</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3620,10 +3638,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3640,13 +3658,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3660,13 +3678,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3683,7 +3701,7 @@
         <v>137</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3703,10 +3721,10 @@
         <v>137</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3720,10 +3738,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>16</v>
@@ -3731,62 +3749,62 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3800,73 +3818,73 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3880,13 +3898,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3900,13 +3918,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3920,10 +3938,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>12</v>
@@ -3940,10 +3958,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>12</v>
@@ -3960,10 +3978,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>12</v>
@@ -3971,19 +3989,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>12</v>
@@ -3991,19 +4009,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>12</v>
@@ -4011,19 +4029,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>12</v>
@@ -4040,10 +4058,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>12</v>
@@ -4060,13 +4078,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4080,13 +4098,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -4100,30 +4118,30 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -4131,19 +4149,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -4151,19 +4169,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>5</v>
@@ -4180,10 +4198,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -4200,10 +4218,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4220,10 +4238,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4240,10 +4258,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4251,19 +4269,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4271,19 +4289,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4291,19 +4309,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4320,10 +4338,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4340,10 +4358,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4360,10 +4378,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4371,19 +4389,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>294</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4391,19 +4409,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4411,19 +4429,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4440,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4460,10 +4478,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4471,19 +4489,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4491,19 +4509,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4511,19 +4529,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="C142" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E142" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4540,13 +4558,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4560,10 +4578,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4571,19 +4589,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4591,19 +4609,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
@@ -4611,19 +4629,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4640,10 +4658,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4660,30 +4678,30 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4691,19 +4709,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4711,19 +4729,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4740,10 +4758,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4760,10 +4778,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4780,10 +4798,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4791,19 +4809,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4811,19 +4829,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4831,19 +4849,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4860,10 +4878,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4880,10 +4898,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4891,19 +4909,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4911,19 +4929,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4931,19 +4949,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4960,10 +4978,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4980,10 +4998,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5000,10 +5018,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5011,19 +5029,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5031,19 +5049,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5051,19 +5069,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5080,10 +5098,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5100,10 +5118,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5120,70 +5138,70 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>16</v>
@@ -5200,70 +5218,70 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5280,10 +5298,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5300,10 +5318,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -5320,10 +5338,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -5331,59 +5349,59 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B185" s="1" t="s">
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5400,13 +5418,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5420,73 +5438,73 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>412</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="E190" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5500,13 +5518,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -5520,13 +5538,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -5540,13 +5558,13 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5560,13 +5578,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5580,12 +5598,72 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E195" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F195" s="1" t="s">
+      <c r="F196" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F197" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F198" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/E/MBF04S.xlsx
+++ b/E/MBF04S.xlsx
@@ -3584,7 +3584,7 @@
         <v>32</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">

--- a/E/MBF04S.xlsx
+++ b/E/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="433">
   <si>
     <t/>
   </si>
@@ -535,6 +535,18 @@
     <t>INDMLK CRM MTCHA 260</t>
   </si>
   <si>
+    <t>20140647</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS COKLAT260</t>
+  </si>
+  <si>
+    <t>20140646</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS PUTIH 260</t>
+  </si>
+  <si>
     <t>20136510</t>
   </si>
   <si>
@@ -577,6 +589,33 @@
     <t>DIABETASOL VNL.170GR</t>
   </si>
   <si>
+    <t>20142907</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 MDU 600</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142908</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 VNL 900</t>
+  </si>
+  <si>
+    <t>20142909</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 VNL 600</t>
+  </si>
+  <si>
+    <t>20142910</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 MDU 900</t>
+  </si>
+  <si>
     <t>20070110</t>
   </si>
   <si>
@@ -607,33 +646,6 @@
     <t>VIDORAN XM5+ COKL700</t>
   </si>
   <si>
-    <t>20142907</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 MDU 600</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
-    <t>20142909</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 VNL 600</t>
-  </si>
-  <si>
-    <t>20142910</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 MDU 900</t>
-  </si>
-  <si>
-    <t>20142908</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 VNL 900</t>
-  </si>
-  <si>
     <t>20098371</t>
   </si>
   <si>
@@ -1286,12 +1298,6 @@
   </si>
   <si>
     <t>HLTHYWY1+ SP MADU700</t>
-  </si>
-  <si>
-    <t>20125790</t>
-  </si>
-  <si>
-    <t>HLTHYWY3+ SB MADU700</t>
   </si>
   <si>
     <t>20089819</t>
@@ -1696,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F198"/>
+  <dimension ref="A1:F203"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3278,13 +3284,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>134</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,10 +3304,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>16</v>
@@ -3321,10 +3327,10 @@
         <v>32</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3341,10 +3347,10 @@
         <v>32</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3361,10 +3367,10 @@
         <v>32</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3381,10 +3387,10 @@
         <v>32</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3401,7 +3407,7 @@
         <v>32</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>12</v>
@@ -3418,10 +3424,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3438,13 +3444,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3458,73 +3464,73 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>200</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3541,10 +3547,10 @@
         <v>38</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>200</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3561,10 +3567,10 @@
         <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3581,10 +3587,10 @@
         <v>38</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3598,10 +3604,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3618,150 +3624,150 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>137</v>
+        <v>38</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3769,79 +3775,79 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>134</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>63</v>
@@ -3849,59 +3855,59 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>229</v>
+        <v>137</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>238</v>
+        <v>137</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>238</v>
+        <v>137</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>16</v>
@@ -3909,19 +3915,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>16</v>
@@ -3929,139 +3935,139 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>12</v>
@@ -4069,19 +4075,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>12</v>
@@ -4089,19 +4095,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>12</v>
@@ -4109,19 +4115,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>12</v>
@@ -4129,139 +4135,139 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4269,19 +4275,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4289,19 +4295,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4309,19 +4315,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4329,19 +4335,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4349,19 +4355,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4369,19 +4375,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4389,19 +4395,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4409,19 +4415,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4429,16 +4435,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>4</v>
@@ -4449,16 +4455,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>8</v>
@@ -4469,16 +4475,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>11</v>
@@ -4489,16 +4495,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>15</v>
@@ -4509,16 +4515,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>19</v>
@@ -4529,19 +4535,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4549,19 +4555,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4569,19 +4575,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4589,19 +4595,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4609,39 +4615,39 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4649,19 +4655,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4669,39 +4675,39 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4709,19 +4715,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4729,39 +4735,39 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4769,19 +4775,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4789,39 +4795,39 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4829,19 +4835,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4849,16 +4855,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>4</v>
@@ -4869,16 +4875,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>8</v>
@@ -4889,16 +4895,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>11</v>
@@ -4909,16 +4915,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>15</v>
@@ -4929,16 +4935,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>19</v>
@@ -4949,19 +4955,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4969,19 +4975,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4989,19 +4995,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5009,19 +5015,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5029,19 +5035,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5049,19 +5055,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5069,16 +5075,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>4</v>
@@ -5089,16 +5095,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>8</v>
@@ -5109,16 +5115,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>11</v>
@@ -5129,16 +5135,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>15</v>
@@ -5149,16 +5155,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>19</v>
@@ -5169,16 +5175,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>23</v>
@@ -5189,99 +5195,99 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5289,19 +5295,19 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5309,96 +5315,96 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>4</v>
@@ -5409,56 +5415,56 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>15</v>
@@ -5469,16 +5475,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>19</v>
@@ -5489,19 +5495,19 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5509,79 +5515,79 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>5</v>
@@ -5589,19 +5595,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5609,19 +5615,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5629,19 +5635,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>137</v>
+        <v>11</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>20</v>
@@ -5649,21 +5655,121 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E199" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F199" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="B202" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F198" s="1" t="s">
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F203" s="1" t="s">
         <v>16</v>
       </c>
     </row>

--- a/E/MBF04S.xlsx
+++ b/E/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="432">
   <si>
     <t/>
   </si>
@@ -595,9 +595,6 @@
     <t>MILKOW A/G 1 MDU 600</t>
   </si>
   <si>
-    <t>,(E-1B)</t>
-  </si>
-  <si>
     <t>20142908</t>
   </si>
   <si>
@@ -733,6 +730,12 @@
     <t>VIDORAN XM5+ MADU700</t>
   </si>
   <si>
+    <t>20125788</t>
+  </si>
+  <si>
+    <t>HLTHYWY1+ SP MADU700</t>
+  </si>
+  <si>
     <t>20032058</t>
   </si>
   <si>
@@ -1292,12 +1295,6 @@
   </si>
   <si>
     <t>SGM EKSPL3+ CKLT 400</t>
-  </si>
-  <si>
-    <t>20125788</t>
-  </si>
-  <si>
-    <t>HLTHYWY1+ SP MADU700</t>
   </si>
   <si>
     <t>20089819</t>
@@ -3470,15 +3467,15 @@
         <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3495,10 +3492,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3510,15 +3507,15 @@
         <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3535,10 +3532,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3555,10 +3552,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3575,10 +3572,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3595,10 +3592,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3615,10 +3612,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3650,15 +3647,15 @@
         <v>23</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>198</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3670,15 +3667,15 @@
         <v>26</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3695,10 +3692,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3715,10 +3712,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>212</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3735,10 +3732,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3755,10 +3752,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3775,10 +3772,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3795,10 +3792,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3815,10 +3812,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3835,10 +3832,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3855,10 +3852,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3875,10 +3872,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3895,10 +3892,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3915,16 +3912,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>4</v>
@@ -3935,16 +3932,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>8</v>
@@ -3955,16 +3952,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>11</v>
@@ -3975,16 +3972,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>15</v>
@@ -3995,59 +3992,59 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>16</v>
@@ -4055,39 +4052,39 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>12</v>
@@ -4095,19 +4092,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>12</v>
@@ -4115,19 +4112,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>12</v>
@@ -4135,19 +4132,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>12</v>
@@ -4155,19 +4152,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>12</v>
@@ -4175,19 +4172,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>12</v>
@@ -4195,19 +4192,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>12</v>
@@ -4215,19 +4212,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>12</v>
@@ -4235,19 +4232,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>12</v>
@@ -4255,39 +4252,39 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4295,19 +4292,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4315,19 +4312,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4335,19 +4332,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4355,19 +4352,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4375,19 +4372,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4395,19 +4392,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4415,19 +4412,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4435,19 +4432,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4455,19 +4452,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4475,19 +4472,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4495,19 +4492,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4515,19 +4512,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4535,19 +4532,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4555,19 +4552,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4575,19 +4572,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4595,19 +4592,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4615,19 +4612,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4635,19 +4632,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4655,19 +4652,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4675,19 +4672,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4695,19 +4692,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4715,19 +4712,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4735,59 +4732,59 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4795,59 +4792,59 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>330</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4855,19 +4852,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4875,19 +4872,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4895,19 +4892,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4915,19 +4912,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4935,19 +4932,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4955,19 +4952,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4975,19 +4972,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4995,19 +4992,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5015,19 +5012,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5035,19 +5032,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5055,19 +5052,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5075,19 +5072,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5095,19 +5092,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5115,19 +5112,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5135,19 +5132,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5155,19 +5152,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5175,19 +5172,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5195,19 +5192,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5215,19 +5212,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5235,19 +5232,19 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5255,19 +5252,19 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>5</v>
@@ -5275,19 +5272,19 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>5</v>
@@ -5295,19 +5292,19 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -5315,39 +5312,39 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>16</v>
@@ -5355,19 +5352,19 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>16</v>
@@ -5375,19 +5372,19 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>16</v>
@@ -5395,39 +5392,39 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5435,19 +5432,19 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5455,19 +5452,19 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5475,19 +5472,19 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>5</v>
@@ -5495,19 +5492,19 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>5</v>
@@ -5515,19 +5512,19 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B191" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>5</v>
@@ -5535,39 +5532,39 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B192" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="E192" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>16</v>
@@ -5575,39 +5572,39 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B194" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="B195" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>415</v>
-      </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>5</v>
@@ -5615,19 +5612,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B196" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B196" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>5</v>
@@ -5635,39 +5632,39 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>418</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B198" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B198" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="C198" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>20</v>
@@ -5675,19 +5672,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B199" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="B199" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>20</v>
@@ -5695,39 +5692,39 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="B200" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>426</v>
-      </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B201" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B201" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>5</v>
@@ -5735,19 +5732,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="B202" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B202" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>20</v>
@@ -5755,19 +5752,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B203" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B203" s="1" t="s">
-        <v>432</v>
-      </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>16</v>
